--- a/NECP Scenario/Results/Regional Results/SKYROS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/SKYROS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.244463019345046E-08</v>
+        <v>4.770638653637646E-08</v>
       </c>
       <c r="C3">
-        <v>3.261078059755524E-08</v>
+        <v>4.792743604376974E-08</v>
       </c>
       <c r="D3">
-        <v>0.0015861096145055</v>
+        <v>0.0015889208980781</v>
       </c>
       <c r="E3">
-        <v>0.7762656584016853</v>
+        <v>0.8919576850434047</v>
       </c>
       <c r="F3">
-        <v>0.7762656271280671</v>
+        <v>0.8919576489770802</v>
       </c>
       <c r="G3">
-        <v>0.7746795537085039</v>
+        <v>0.8903687779157052</v>
       </c>
       <c r="H3">
-        <v>0.752422224396219</v>
+        <v>0.844686948331926</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000065766</v>
+        <v>0.4000000000069899</v>
       </c>
       <c r="C13">
-        <v>0.4000000000086192</v>
+        <v>0.40000000000999</v>
       </c>
       <c r="D13">
-        <v>0.4000000000125931</v>
+        <v>0.4000000000158249</v>
       </c>
       <c r="E13">
-        <v>0.4000000000233089</v>
+        <v>0.4000000000287945</v>
       </c>
       <c r="F13">
-        <v>0.4000000000403996</v>
+        <v>0.4000000000493272</v>
       </c>
       <c r="G13">
-        <v>0.4000000000743944</v>
+        <v>0.4000000000945863</v>
       </c>
       <c r="H13">
-        <v>0.4000000004235313</v>
+        <v>0.4000000005045024</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0047214363767306</v>
+        <v>0.0047172578120459</v>
       </c>
       <c r="E27">
-        <v>0.0625085527271695</v>
+        <v>0.0625085526325138</v>
       </c>
       <c r="F27">
-        <v>0.0625085528249887</v>
+        <v>0.0625085527641322</v>
       </c>
       <c r="G27">
-        <v>0.0625085528875344</v>
+        <v>0.062508552849767</v>
       </c>
       <c r="H27">
-        <v>0.0625085529471604</v>
+        <v>0.0625085529293037</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3.606732663103254E-08</v>
+        <v>5.32638015123199E-08</v>
       </c>
       <c r="E29">
-        <v>0.0030437739054376</v>
+        <v>0.0030437747572602</v>
       </c>
       <c r="F29">
-        <v>0.0030437755998244</v>
+        <v>0.0030437755684503</v>
       </c>
       <c r="G29">
-        <v>0.0030437758000284</v>
+        <v>0.0030437757703458</v>
       </c>
       <c r="H29">
-        <v>0.0030437759112495</v>
+        <v>0.0030437758967494</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0039283340252097</v>
+        <v>0.0039279957434786</v>
       </c>
       <c r="E33">
-        <v>0.678434616734123</v>
+        <v>0.6784346166264716</v>
       </c>
       <c r="F33">
-        <v>0.6784346168005525</v>
+        <v>0.6784346167222864</v>
       </c>
       <c r="G33">
-        <v>0.6784346168472927</v>
+        <v>0.6784346167883869</v>
       </c>
       <c r="H33">
-        <v>0.6784346169469618</v>
+        <v>0.6784346169169931</v>
       </c>
     </row>
     <row r="34" spans="1:8">
